--- a/data/lossofsale_sg_thrissur.xlsx
+++ b/data/lossofsale_sg_thrissur.xlsx
@@ -5419,6 +5419,1013 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="65">
+        <v>98</v>
+      </c>
+      <c t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">JOFIN</t>
+        </is>
+      </c>
+      <c r="D100" s="65">
+        <v>9497556486</v>
+      </c>
+      <c t="inlineStr" r="E100">
+        <is>
+          <t xml:space="preserve">12-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F100">
+        <is>
+          <t xml:space="preserve">SHYAMNADH T J</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G100">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H100">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I100">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J100">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K100">
+        <is>
+          <t xml:space="preserve">visit tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="65">
+        <v>99</v>
+      </c>
+      <c t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C101">
+        <is>
+          <t xml:space="preserve">RIXON</t>
+        </is>
+      </c>
+      <c r="D101" s="65">
+        <v>9961335788</v>
+      </c>
+      <c t="inlineStr" r="E101">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F101">
+        <is>
+          <t xml:space="preserve">RASEEB E A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G101">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H101">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I101">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J101">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K101">
+        <is>
+          <t xml:space="preserve">JUST VISITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="65">
+        <v>100</v>
+      </c>
+      <c t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C102">
+        <is>
+          <t xml:space="preserve">LINTO</t>
+        </is>
+      </c>
+      <c r="D102" s="65">
+        <v>8589977235</v>
+      </c>
+      <c t="inlineStr" r="E102">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F102">
+        <is>
+          <t xml:space="preserve">RASEEB E A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G102">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H102">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I102">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J102">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K102">
+        <is>
+          <t xml:space="preserve">JUST VISIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="65">
+        <v>101</v>
+      </c>
+      <c t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C103">
+        <is>
+          <t xml:space="preserve">SEMEER</t>
+        </is>
+      </c>
+      <c r="D103" s="65">
+        <v>8848585933</v>
+      </c>
+      <c t="inlineStr" r="E103">
+        <is>
+          <t xml:space="preserve">04-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F103">
+        <is>
+          <t xml:space="preserve">RASEEB E A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G103">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H103">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I103">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J103">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K103">
+        <is>
+          <t xml:space="preserve">NEED KIDS SUIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="65">
+        <v>102</v>
+      </c>
+      <c t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C104">
+        <is>
+          <t xml:space="preserve">Anas</t>
+        </is>
+      </c>
+      <c r="D104" s="65">
+        <v>9947611544</v>
+      </c>
+      <c t="inlineStr" r="E104">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F104">
+        <is>
+          <t xml:space="preserve">SHYAMNADH T J</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G104">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H104">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I104">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J104">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K104">
+        <is>
+          <t xml:space="preserve">THEY NEED TO VISIT CHAVAKAD STORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="65">
+        <v>103</v>
+      </c>
+      <c t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C105">
+        <is>
+          <t xml:space="preserve">Jomon</t>
+        </is>
+      </c>
+      <c r="D105" s="65">
+        <v>8893428901</v>
+      </c>
+      <c t="inlineStr" r="E105">
+        <is>
+          <t xml:space="preserve">31-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F105">
+        <is>
+          <t xml:space="preserve">ATHULKIRSHNA CS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G105">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H105">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I105">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J105">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K105">
+        <is>
+          <t xml:space="preserve">THEY BOOKED THE PRODUCT BUT PAY THE FULL AMOUNT ON 30TH ON DELIVERY DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="65">
+        <v>104</v>
+      </c>
+      <c t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C106">
+        <is>
+          <t xml:space="preserve">jofin</t>
+        </is>
+      </c>
+      <c r="D106" s="65">
+        <v>8089699530</v>
+      </c>
+      <c t="inlineStr" r="E106">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F106">
+        <is>
+          <t xml:space="preserve">RAYAN K B</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G106">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H106">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I106">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J106">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K106">
+        <is>
+          <t xml:space="preserve">will update later</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="65">
+        <v>105</v>
+      </c>
+      <c t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">SHYAM</t>
+        </is>
+      </c>
+      <c r="D107" s="65">
+        <v>9447992719</v>
+      </c>
+      <c t="inlineStr" r="E107">
+        <is>
+          <t xml:space="preserve">08-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F107">
+        <is>
+          <t xml:space="preserve">MUHAMMED JASIR. V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G107">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H107">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I107">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J107">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K107">
+        <is>
+          <t xml:space="preserve">HE NEED 46,44 SIZE PRODUCTS IN PREMIUM SUITS WE WILL CONNECT HIM AFTER CONNECTING OUR OTHER OUTLETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="65">
+        <v>106</v>
+      </c>
+      <c t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">shilvit</t>
+        </is>
+      </c>
+      <c r="D108" s="65">
+        <v>9526623337</v>
+      </c>
+      <c t="inlineStr" r="E108">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F108">
+        <is>
+          <t xml:space="preserve">SHYAMNADH T J</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G108">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H108">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I108">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J108">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K108">
+        <is>
+          <t xml:space="preserve">KURTHA PURPLE 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="65">
+        <v>107</v>
+      </c>
+      <c t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C109">
+        <is>
+          <t xml:space="preserve">Melvin</t>
+        </is>
+      </c>
+      <c r="D109" s="65">
+        <v>7907429451</v>
+      </c>
+      <c t="inlineStr" r="E109">
+        <is>
+          <t xml:space="preserve">31-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F109">
+        <is>
+          <t xml:space="preserve">RAYAN K B</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G109">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H109">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I109">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J109">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K109">
+        <is>
+          <t xml:space="preserve">will update later</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="65">
+        <v>108</v>
+      </c>
+      <c t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C110">
+        <is>
+          <t xml:space="preserve">Akash</t>
+        </is>
+      </c>
+      <c r="D110" s="65">
+        <v>8553078120</v>
+      </c>
+      <c t="inlineStr" r="E110">
+        <is>
+          <t xml:space="preserve">25-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F110">
+        <is>
+          <t xml:space="preserve">SHYAMNADH T J</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G110">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H110">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I110">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J110">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K110">
+        <is>
+          <t xml:space="preserve">JUST VISIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="65">
+        <v>109</v>
+      </c>
+      <c t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C111">
+        <is>
+          <t xml:space="preserve">suhil</t>
+        </is>
+      </c>
+      <c r="D111" s="65">
+        <v>9544121707</v>
+      </c>
+      <c t="inlineStr" r="E111">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F111">
+        <is>
+          <t xml:space="preserve">RASEEB E A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G111">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H111">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I111">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J111">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K111">
+        <is>
+          <t xml:space="preserve">brown suit not available for today function</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="65">
+        <v>110</v>
+      </c>
+      <c t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C112">
+        <is>
+          <t xml:space="preserve">charles</t>
+        </is>
+      </c>
+      <c r="D112" s="65">
+        <v>9061481913</v>
+      </c>
+      <c t="inlineStr" r="E112">
+        <is>
+          <t xml:space="preserve">26-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F112">
+        <is>
+          <t xml:space="preserve">ATHULKIRSHNA CS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G112">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H112">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I112">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J112">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K112">
+        <is>
+          <t xml:space="preserve">model not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="65">
+        <v>111</v>
+      </c>
+      <c t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C113">
+        <is>
+          <t xml:space="preserve">amanto</t>
+        </is>
+      </c>
+      <c r="D113" s="65">
+        <v>7560814131</v>
+      </c>
+      <c t="inlineStr" r="E113">
+        <is>
+          <t xml:space="preserve">30-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F113">
+        <is>
+          <t xml:space="preserve">ATHULKIRSHNA CS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G113">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H113">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I113">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J113">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K113">
+        <is>
+          <t xml:space="preserve">required product not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="65">
+        <v>112</v>
+      </c>
+      <c t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">nithin</t>
+        </is>
+      </c>
+      <c r="D114" s="65">
+        <v>9567450118</v>
+      </c>
+      <c t="inlineStr" r="E114">
+        <is>
+          <t xml:space="preserve">25-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F114">
+        <is>
+          <t xml:space="preserve">RAYAN K B</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G114">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H114">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I114">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J114">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K114">
+        <is>
+          <t xml:space="preserve">one suide suit 42 not available for trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="65">
+        <v>113</v>
+      </c>
+      <c t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C115">
+        <is>
+          <t xml:space="preserve">TIJO</t>
+        </is>
+      </c>
+      <c r="D115" s="65">
+        <v>9995565546</v>
+      </c>
+      <c t="inlineStr" r="E115">
+        <is>
+          <t xml:space="preserve">17-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F115">
+        <is>
+          <t xml:space="preserve">SHYAMNADH T J</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G115">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H115">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I115">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J115">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K115">
+        <is>
+          <t xml:space="preserve">BLACK EMBRO 38,38 One side work</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="65">
+        <v>114</v>
+      </c>
+      <c t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C116">
+        <is>
+          <t xml:space="preserve">Rahul</t>
+        </is>
+      </c>
+      <c r="D116" s="65">
+        <v>8848958908</v>
+      </c>
+      <c t="inlineStr" r="E116">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F116">
+        <is>
+          <t xml:space="preserve">RAYAN K B</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G116">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H116">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I116">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J116">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K116">
+        <is>
+          <t xml:space="preserve">kids suit</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="65">
+        <v>115</v>
+      </c>
+      <c t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C117">
+        <is>
+          <t xml:space="preserve">abhishek</t>
+        </is>
+      </c>
+      <c r="D117" s="65">
+        <v>8111848784</v>
+      </c>
+      <c t="inlineStr" r="E117">
+        <is>
+          <t xml:space="preserve">23-08-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F117">
+        <is>
+          <t xml:space="preserve">RASEEB E A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G117">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H117">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I117">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J117">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K117">
+        <is>
+          <t xml:space="preserve">just visiting for brother</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="65">
+        <v>116</v>
+      </c>
+      <c t="inlineStr" r="B118">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C118">
+        <is>
+          <t xml:space="preserve">jofin</t>
+        </is>
+      </c>
+      <c r="D118" s="65">
+        <v>9074809340</v>
+      </c>
+      <c t="inlineStr" r="E118">
+        <is>
+          <t xml:space="preserve">03-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F118">
+        <is>
+          <t xml:space="preserve">ATHULKIRSHNA CS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G118">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H118">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I118">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J118">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K118">
+        <is>
+          <t xml:space="preserve">beach colour plan suit needed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
